--- a/templates/allergen/template_diner.xlsx
+++ b/templates/allergen/template_diner.xlsx
@@ -1038,11 +1038,7 @@
       <c r="R15" s="35" t="n"/>
     </row>
     <row r="16" ht="17.25" customHeight="1" s="24">
-      <c r="A16" s="44" t="inlineStr">
-        <is>
-          <t>Végétaliens</t>
-        </is>
-      </c>
+      <c r="A16" s="44" t="inlineStr"/>
       <c r="B16" s="39" t="inlineStr">
         <is>
           <t>Soupe à l'oignon</t>
@@ -1272,7 +1268,7 @@
     <row r="24" ht="17.25" customHeight="1" s="24">
       <c r="A24" s="38" t="inlineStr">
         <is>
-          <t>Spéciaux</t>
+          <t>Spéciaux avec lactose</t>
         </is>
       </c>
       <c r="B24" s="39" t="inlineStr">

--- a/templates/allergen/template_diner.xlsx
+++ b/templates/allergen/template_diner.xlsx
@@ -1038,7 +1038,11 @@
       <c r="R15" s="35" t="n"/>
     </row>
     <row r="16" ht="17.25" customHeight="1" s="24">
-      <c r="A16" s="44" t="inlineStr"/>
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>Végétaliens</t>
+        </is>
+      </c>
       <c r="B16" s="39" t="inlineStr">
         <is>
           <t>Soupe à l'oignon</t>
@@ -1268,7 +1272,7 @@
     <row r="24" ht="17.25" customHeight="1" s="24">
       <c r="A24" s="38" t="inlineStr">
         <is>
-          <t>Spéciaux avec lactose</t>
+          <t>Spéciaux</t>
         </is>
       </c>
       <c r="B24" s="39" t="inlineStr">
